--- a/25-26/proforma Invoice/Proforma Invoice (Format ) final.xlsx
+++ b/25-26/proforma Invoice/Proforma Invoice (Format ) final.xlsx
@@ -169,18 +169,18 @@
     <t>Any Port Of Vietnam</t>
   </si>
   <si>
-    <t>HOANG MINH STONE TRADING COMPANY LIMITED
-Lot 175 MBQH 6804 Hac Thanh Ward, Thanh Hoa 
-Province
- Tax ID: 2803146553
- TEL:  0392794691
- hoangminh6868vn@gmail.com</t>
-  </si>
-  <si>
-    <t>PI0112/25-26</t>
-  </si>
-  <si>
-    <t>5% advance</t>
+    <t>CMK TRADING COMPANY LIMITED
+ADD: No 60 street 64-TML, Quarter 1, Cat Lai Ward, 
+Ho Chi Minh city, Vietnam
+TAX ID : 0317762127
+PHONE : +84 974778685
+EMAIL : cmktrading.coltd@gmail.com</t>
+  </si>
+  <si>
+    <t>1100 $ advance remaining against documents</t>
+  </si>
+  <si>
+    <t>YX2026040201</t>
   </si>
 </sst>
 </file>
@@ -1167,7 +1167,7 @@
       <c r="H3" s="41"/>
       <c r="I3" s="42"/>
       <c r="J3" s="83" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K3" s="84"/>
     </row>
@@ -1185,7 +1185,7 @@
       <c r="H4" s="41"/>
       <c r="I4" s="42"/>
       <c r="J4" s="85">
-        <v>45992</v>
+        <v>46137</v>
       </c>
       <c r="K4" s="84"/>
     </row>
@@ -1203,7 +1203,7 @@
       <c r="H5" s="41"/>
       <c r="I5" s="42"/>
       <c r="J5" s="85">
-        <v>46006</v>
+        <v>46152</v>
       </c>
       <c r="K5" s="84"/>
     </row>
@@ -1373,7 +1373,7 @@
       <c r="H15" s="28"/>
       <c r="I15" s="29"/>
       <c r="J15" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K15" s="35"/>
     </row>
@@ -1451,14 +1451,14 @@
         <v>68022390</v>
       </c>
       <c r="I19" s="20">
-        <v>400</v>
+        <v>429</v>
       </c>
       <c r="J19" s="21">
-        <v>15.75</v>
+        <v>26.5</v>
       </c>
       <c r="K19" s="22">
         <f>I19*J19</f>
-        <v>6300</v>
+        <v>11368.5</v>
       </c>
       <c r="N19" s="8"/>
       <c r="O19" s="8"/>
@@ -1495,7 +1495,7 @@
       <c r="J21" s="78"/>
       <c r="K21" s="69">
         <f>SUM(K19:K20)</f>
-        <v>6300</v>
+        <v>11368.5</v>
       </c>
     </row>
     <row r="22" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1542,7 +1542,7 @@
       <c r="J24" s="73"/>
       <c r="K24" s="71">
         <f>K21</f>
-        <v>6300</v>
+        <v>11368.5</v>
       </c>
     </row>
     <row r="25" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
